--- a/ProjectDescription/DownloadTask_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadTask_FunctionNameReg.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,120 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>downloadedBytes</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>已下载字节数，从进度文件实时更新，持久化保存</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/DownloadTask.java)[DownloadTask:36]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>getDownloadedBytes/setDownloadedBytes获取和设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>totalBytesForProgress</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>总字节数，从进度文件实时更新，持久化保存</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/DownloadTask.java)[DownloadTask:37]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>getTotalBytesForProgress/setTotalBytesForProgress获取和设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>下载速度（字节/秒），仅运行时使用，不持久化</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/model/DownloadTask.java)[DownloadTask:38]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>getSpeed/setSpeed获取和设置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
